--- a/main/StructureDefinition-Consent.xlsx
+++ b/main/StructureDefinition-Consent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$148</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5206" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5348" uniqueCount="616">
   <si>
     <t>Property</t>
   </si>
@@ -560,7 +560,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -650,6 +650,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Consent.extension:domainReference.id</t>
   </si>
   <si>
@@ -961,7 +965,7 @@
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://acme.org/identifier/local/eCMS"/&gt;
+  &lt;system value="urn:ietf:rfc:3986"/&gt;
   &lt;value value="Local eCMS identifier"/&gt;
 &lt;/valueIdentifier&gt;</t>
   </si>
@@ -1028,12 +1032,15 @@
     <t>The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
   </si>
   <si>
     <t>Consent.category</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Classification of the consent statement - for indexing/retrieval</t>
   </si>
   <si>
@@ -1043,7 +1050,7 @@
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1326,7 +1333,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1404,7 +1411,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1433,7 +1440,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1559,7 +1566,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
   </si>
   <si>
     <t>Consent.policyRule.id</t>
@@ -1578,6 +1585,37 @@
 </t>
   </si>
   <si>
+    <t>Consent.policyRule.extension:xacml.id</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension.id</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension:xacml.extension</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension.extension</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension:xacml.url</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension.url</t>
+  </si>
+  <si>
+    <t>http://fhir.de/ConsentManagement/StructureDefinition/Xacml</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension:xacml.value[x]</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
     <t>Consent.policyRule.coding</t>
   </si>
   <si>
@@ -1614,7 +1652,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1712,13 +1750,13 @@
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1746,7 +1784,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1761,6 +1799,9 @@
     <t>If the consent specifies a security label of "R" then it applies to all resources that are labeled "R" or lower. E.g. for Confidentiality, it's a high water mark. For other kinds of security labels, subsumption logic applies. When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
     <t>Consent.provision.purpose</t>
   </si>
   <si>
@@ -1794,7 +1835,7 @@
     <t>The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1812,7 +1853,7 @@
     <t>If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1866,7 +1907,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -2205,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN144"/>
+  <dimension ref="A1:AN148"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
@@ -2227,7 +2268,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="47.265625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="36.39453125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
@@ -4400,7 +4441,7 @@
         <v>202</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4417,10 +4458,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4529,10 +4570,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4641,13 +4682,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="C22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>20</v>
@@ -4755,10 +4796,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4867,10 +4908,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4981,10 +5022,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5010,13 +5051,13 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5024,7 +5065,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>20</v>
@@ -5066,7 +5107,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -5095,10 +5136,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5121,13 +5162,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5178,7 +5219,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -5207,13 +5248,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
@@ -5321,10 +5362,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5433,10 +5474,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5547,10 +5588,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5576,13 +5617,13 @@
         <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5590,7 +5631,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>20</v>
@@ -5632,7 +5673,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5661,10 +5702,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5690,10 +5731,10 @@
         <v>147</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5720,11 +5761,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5742,7 +5783,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5771,10 +5812,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5883,10 +5924,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5997,10 +6038,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6026,16 +6067,16 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6084,7 +6125,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6102,10 +6143,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6113,10 +6154,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6142,13 +6183,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6198,7 +6239,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6216,10 +6257,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6227,10 +6268,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6256,14 +6297,14 @@
         <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6312,7 +6353,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6330,10 +6371,10 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -6341,10 +6382,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6370,14 +6411,14 @@
         <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6426,7 +6467,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6444,10 +6485,10 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6455,10 +6496,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6481,19 +6522,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6542,7 +6583,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6560,10 +6601,10 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6571,10 +6612,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6600,13 +6641,13 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6614,7 +6655,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>20</v>
@@ -6656,7 +6697,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>88</v>
@@ -6685,10 +6726,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6711,13 +6752,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6768,7 +6809,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6797,13 +6838,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
@@ -6825,13 +6866,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6911,13 +6952,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
@@ -6939,13 +6980,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7025,10 +7066,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7054,16 +7095,16 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7112,7 +7153,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7141,10 +7182,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7167,16 +7208,16 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7190,7 +7231,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -7226,7 +7267,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7241,24 +7282,24 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7284,16 +7325,16 @@
         <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7318,13 +7359,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7342,7 +7383,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -7357,24 +7398,24 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7397,16 +7438,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7435,10 +7476,10 @@
         <v>151</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7456,7 +7497,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>88</v>
@@ -7485,10 +7526,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7496,7 +7537,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>328</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>78</v>
@@ -7511,13 +7552,13 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7547,16 +7588,16 @@
         <v>151</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7566,7 +7607,7 @@
         <v>115</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>88</v>
@@ -7581,27 +7622,27 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7623,13 +7664,13 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7659,10 +7700,10 @@
         <v>151</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7680,7 +7721,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>88</v>
@@ -7695,24 +7736,24 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7821,10 +7862,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7935,10 +7976,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7964,16 +8005,16 @@
         <v>147</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8022,7 +8063,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8040,10 +8081,10 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -8051,10 +8092,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8163,10 +8204,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8277,10 +8318,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8306,16 +8347,16 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8364,7 +8405,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8382,10 +8423,10 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8393,10 +8434,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8422,13 +8463,13 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8478,7 +8519,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8496,10 +8537,10 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8507,10 +8548,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8536,14 +8577,14 @@
         <v>169</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8592,7 +8633,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8610,10 +8651,10 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8621,10 +8662,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8650,14 +8691,14 @@
         <v>102</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8706,7 +8747,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8724,10 +8765,10 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -8735,10 +8776,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8761,19 +8802,19 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8822,7 +8863,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8840,10 +8881,10 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
@@ -8851,10 +8892,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8880,16 +8921,16 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8938,7 +8979,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8956,10 +8997,10 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -8967,20 +9008,20 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>78</v>
@@ -8995,13 +9036,13 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9028,11 +9069,11 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9050,7 +9091,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>88</v>
@@ -9065,24 +9106,24 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9191,10 +9232,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9305,10 +9346,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9334,16 +9375,16 @@
         <v>147</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9392,7 +9433,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9410,10 +9451,10 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -9421,10 +9462,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9533,10 +9574,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9647,10 +9688,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9676,16 +9717,16 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9734,7 +9775,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9752,10 +9793,10 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
@@ -9763,10 +9804,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9792,13 +9833,13 @@
         <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9848,7 +9889,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9866,10 +9907,10 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
@@ -9877,10 +9918,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9906,14 +9947,14 @@
         <v>169</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9962,7 +10003,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9980,10 +10021,10 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -9991,10 +10032,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10020,14 +10061,14 @@
         <v>102</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10076,7 +10117,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10094,10 +10135,10 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -10105,10 +10146,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10131,19 +10172,19 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10192,7 +10233,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10210,10 +10251,10 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>20</v>
@@ -10221,10 +10262,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10250,16 +10291,16 @@
         <v>102</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10308,7 +10349,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10326,10 +10367,10 @@
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
@@ -10337,20 +10378,20 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>78</v>
@@ -10365,13 +10406,13 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10402,7 +10443,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10420,7 +10461,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>88</v>
@@ -10435,24 +10476,24 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10561,10 +10602,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10675,10 +10716,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10704,16 +10745,16 @@
         <v>147</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10762,7 +10803,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10780,10 +10821,10 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>20</v>
@@ -10791,10 +10832,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10903,10 +10944,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11017,10 +11058,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11046,16 +11087,16 @@
         <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11104,7 +11145,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -11122,10 +11163,10 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>20</v>
@@ -11133,10 +11174,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11162,13 +11203,13 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11218,7 +11259,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11236,10 +11277,10 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>20</v>
@@ -11247,10 +11288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11276,14 +11317,14 @@
         <v>169</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11332,7 +11373,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11350,10 +11391,10 @@
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>20</v>
@@ -11361,10 +11402,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11390,14 +11431,14 @@
         <v>102</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11446,7 +11487,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11464,10 +11505,10 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>20</v>
@@ -11475,10 +11516,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11501,19 +11542,19 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11562,7 +11603,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11580,10 +11621,10 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>20</v>
@@ -11591,10 +11632,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11620,16 +11661,16 @@
         <v>102</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11678,7 +11719,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11696,10 +11737,10 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>20</v>
@@ -11707,10 +11748,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11733,16 +11774,16 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11792,7 +11833,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11807,24 +11848,24 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11933,10 +11974,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12047,10 +12088,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12076,13 +12117,13 @@
         <v>102</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12132,7 +12173,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12141,7 +12182,7 @@
         <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>100</v>
@@ -12161,10 +12202,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12190,13 +12231,13 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12225,10 +12266,10 @@
         <v>151</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12246,7 +12287,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12275,10 +12316,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12301,16 +12342,16 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12360,7 +12401,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12381,7 +12422,7 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>20</v>
@@ -12389,10 +12430,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12418,13 +12459,13 @@
         <v>102</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12474,7 +12515,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12503,10 +12544,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12529,16 +12570,16 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12588,7 +12629,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12603,28 +12644,28 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12643,16 +12684,16 @@
         <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12702,7 +12743,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12717,28 +12758,28 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12757,13 +12798,13 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12814,7 +12855,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12829,7 +12870,7 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>20</v>
@@ -12838,15 +12879,15 @@
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12869,16 +12910,16 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12928,7 +12969,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12946,7 +12987,7 @@
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>20</v>
@@ -12957,10 +12998,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13069,10 +13110,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13183,10 +13224,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13212,13 +13253,13 @@
         <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13268,7 +13309,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13277,7 +13318,7 @@
         <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>100</v>
@@ -13297,10 +13338,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13326,13 +13367,13 @@
         <v>135</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13361,10 +13402,10 @@
         <v>151</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>20</v>
@@ -13382,7 +13423,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13411,10 +13452,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13437,16 +13478,16 @@
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13496,7 +13537,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13517,7 +13558,7 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>20</v>
@@ -13525,10 +13566,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13554,13 +13595,13 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13610,7 +13651,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13639,10 +13680,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13665,13 +13706,13 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13722,7 +13763,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13751,10 +13792,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13863,10 +13904,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13977,14 +14018,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14006,16 +14047,16 @@
         <v>109</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -14064,7 +14105,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -14093,10 +14134,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14122,10 +14163,10 @@
         <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14176,7 +14217,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14185,7 +14226,7 @@
         <v>88</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>100</v>
@@ -14205,10 +14246,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14234,13 +14275,13 @@
         <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14290,7 +14331,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14299,7 +14340,7 @@
         <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>100</v>
@@ -14319,10 +14360,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14345,19 +14386,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -14385,10 +14426,10 @@
         <v>151</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14406,7 +14447,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14415,7 +14456,7 @@
         <v>88</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>100</v>
@@ -14435,10 +14476,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14547,10 +14588,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14659,13 +14700,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>20</v>
@@ -14687,7 +14728,7 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>200</v>
@@ -14773,10 +14814,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14787,7 +14828,7 @@
         <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>20</v>
@@ -14796,23 +14837,19 @@
         <v>20</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>20</v>
       </c>
@@ -14860,28 +14897,28 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>348</v>
+        <v>105</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>350</v>
+        <v>106</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>20</v>
@@ -14889,21 +14926,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>20</v>
@@ -14912,23 +14949,21 @@
         <v>20</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>367</v>
+        <v>110</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>368</v>
+        <v>111</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>20</v>
       </c>
@@ -14964,40 +14999,40 @@
         <v>20</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>371</v>
+        <v>116</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>373</v>
+        <v>106</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>20</v>
@@ -15005,10 +15040,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15016,10 +15051,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>20</v>
@@ -15028,25 +15063,27 @@
         <v>20</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>473</v>
+        <v>135</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>505</v>
+        <v>216</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>20</v>
+        <v>510</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>20</v>
@@ -15088,19 +15125,19 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>504</v>
+        <v>219</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>20</v>
@@ -15109,7 +15146,7 @@
         <v>20</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>20</v>
@@ -15117,10 +15154,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15128,7 +15165,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>88</v>
@@ -15143,13 +15180,13 @@
         <v>20</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>102</v>
+        <v>513</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>103</v>
+        <v>223</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>104</v>
+        <v>224</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15200,7 +15237,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15212,7 +15249,7 @@
         <v>20</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>20</v>
@@ -15221,7 +15258,7 @@
         <v>20</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>20</v>
@@ -15229,14 +15266,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15252,21 +15289,23 @@
         <v>20</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>110</v>
+        <v>346</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>111</v>
+        <v>347</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
       </c>
@@ -15314,7 +15353,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>116</v>
+        <v>350</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15326,16 +15365,16 @@
         <v>20</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>106</v>
+        <v>352</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>20</v>
@@ -15343,45 +15382,45 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J116" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>480</v>
+        <v>369</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>481</v>
+        <v>370</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>112</v>
+        <v>371</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -15430,28 +15469,28 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>482</v>
+        <v>373</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>192</v>
+        <v>375</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>20</v>
@@ -15459,10 +15498,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15470,10 +15509,10 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>20</v>
@@ -15485,13 +15524,13 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>272</v>
+        <v>475</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15542,13 +15581,13 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>20</v>
@@ -15571,10 +15610,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15597,13 +15636,13 @@
         <v>20</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>514</v>
+        <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>515</v>
+        <v>103</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>516</v>
+        <v>104</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15654,7 +15693,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>513</v>
+        <v>105</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15666,7 +15705,7 @@
         <v>20</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>20</v>
@@ -15675,7 +15714,7 @@
         <v>20</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>20</v>
@@ -15683,21 +15722,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>20</v>
@@ -15709,15 +15748,17 @@
         <v>20</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>437</v>
+        <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>518</v>
+        <v>110</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>20</v>
@@ -15766,19 +15807,19 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>517</v>
+        <v>116</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>20</v>
@@ -15787,50 +15828,54 @@
         <v>20</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I120" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="J120" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>473</v>
+        <v>109</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>521</v>
+        <v>482</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>20</v>
       </c>
@@ -15878,19 +15923,19 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>520</v>
+        <v>484</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>20</v>
@@ -15899,7 +15944,7 @@
         <v>20</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>20</v>
@@ -15907,10 +15952,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15918,7 +15963,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>88</v>
@@ -15930,16 +15975,16 @@
         <v>20</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>102</v>
+        <v>273</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>103</v>
+        <v>523</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>104</v>
+        <v>524</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15990,10 +16035,10 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>88</v>
@@ -16002,7 +16047,7 @@
         <v>20</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>20</v>
@@ -16011,7 +16056,7 @@
         <v>20</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>20</v>
@@ -16019,21 +16064,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>20</v>
@@ -16045,17 +16090,15 @@
         <v>20</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>109</v>
+        <v>526</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>110</v>
+        <v>527</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -16104,19 +16147,19 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>116</v>
+        <v>525</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>20</v>
@@ -16125,7 +16168,7 @@
         <v>20</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>20</v>
@@ -16133,46 +16176,42 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>20</v>
       </c>
@@ -16220,19 +16259,19 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>482</v>
+        <v>529</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>20</v>
@@ -16241,18 +16280,18 @@
         <v>20</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16266,7 +16305,7 @@
         <v>88</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>20</v>
@@ -16275,13 +16314,13 @@
         <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>169</v>
+        <v>475</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16308,13 +16347,13 @@
         <v>20</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>529</v>
+        <v>20</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>530</v>
+        <v>20</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -16332,7 +16371,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -16359,12 +16398,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16378,22 +16417,22 @@
         <v>88</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>532</v>
+        <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>533</v>
+        <v>103</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16444,7 +16483,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>531</v>
+        <v>105</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16456,7 +16495,7 @@
         <v>20</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>20</v>
@@ -16465,7 +16504,7 @@
         <v>20</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>20</v>
@@ -16473,14 +16512,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -16499,22 +16538,22 @@
         <v>20</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>473</v>
+        <v>109</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>536</v>
+        <v>110</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q126" t="s" s="2">
-        <v>538</v>
-      </c>
+      <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
         <v>20</v>
       </c>
@@ -16558,7 +16597,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>535</v>
+        <v>116</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16570,7 +16609,7 @@
         <v>20</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>20</v>
@@ -16579,7 +16618,7 @@
         <v>20</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>20</v>
@@ -16587,42 +16626,46 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>103</v>
+        <v>482</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>20</v>
       </c>
@@ -16670,19 +16713,19 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>105</v>
+        <v>484</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>20</v>
@@ -16691,7 +16734,7 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>20</v>
@@ -16699,21 +16742,21 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>20</v>
@@ -16722,20 +16765,18 @@
         <v>20</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>110</v>
+        <v>539</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -16760,13 +16801,13 @@
         <v>20</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>20</v>
+        <v>541</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>20</v>
+        <v>542</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>20</v>
@@ -16784,19 +16825,19 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>116</v>
+        <v>538</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>20</v>
@@ -16805,54 +16846,50 @@
         <v>20</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J129" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>109</v>
+        <v>544</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>480</v>
+        <v>545</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>20</v>
       </c>
@@ -16900,19 +16937,19 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>482</v>
+        <v>543</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>20</v>
@@ -16921,7 +16958,7 @@
         <v>20</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>20</v>
@@ -16929,10 +16966,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16940,10 +16977,10 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>20</v>
@@ -16955,20 +16992,22 @@
         <v>20</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>320</v>
+        <v>475</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q130" s="2"/>
+      <c r="Q130" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="R130" t="s" s="2">
         <v>20</v>
       </c>
@@ -16988,13 +17027,13 @@
         <v>20</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>545</v>
+        <v>20</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>546</v>
+        <v>20</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>20</v>
@@ -17012,13 +17051,13 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>20</v>
@@ -17041,10 +17080,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17052,7 +17091,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>88</v>
@@ -17067,13 +17106,13 @@
         <v>20</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>548</v>
+        <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>549</v>
+        <v>103</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>550</v>
+        <v>104</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17124,10 +17163,10 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>547</v>
+        <v>105</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>88</v>
@@ -17136,7 +17175,7 @@
         <v>20</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>20</v>
@@ -17145,7 +17184,7 @@
         <v>20</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>20</v>
@@ -17153,14 +17192,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17176,27 +17215,25 @@
         <v>20</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>320</v>
+        <v>109</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>552</v>
+        <v>110</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>553</v>
+        <v>111</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q132" t="s" s="2">
-        <v>555</v>
-      </c>
+      <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
         <v>20</v>
       </c>
@@ -17216,13 +17253,13 @@
         <v>20</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>556</v>
+        <v>20</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>557</v>
+        <v>20</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>20</v>
@@ -17240,7 +17277,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>551</v>
+        <v>116</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -17252,7 +17289,7 @@
         <v>20</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>20</v>
@@ -17261,7 +17298,7 @@
         <v>20</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>20</v>
@@ -17269,14 +17306,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -17289,24 +17326,26 @@
         <v>20</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J133" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>559</v>
+        <v>482</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>560</v>
+        <v>483</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>20</v>
       </c>
@@ -17330,13 +17369,13 @@
         <v>20</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>20</v>
@@ -17354,7 +17393,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>558</v>
+        <v>484</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -17366,7 +17405,7 @@
         <v>20</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>20</v>
@@ -17375,7 +17414,7 @@
         <v>20</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>20</v>
@@ -17383,10 +17422,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17394,10 +17433,10 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>20</v>
@@ -17406,20 +17445,18 @@
         <v>20</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>147</v>
+        <v>321</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -17447,10 +17484,10 @@
         <v>151</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>20</v>
@@ -17468,13 +17505,13 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>20</v>
@@ -17497,10 +17534,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17508,10 +17545,10 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>20</v>
@@ -17520,20 +17557,18 @@
         <v>20</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>147</v>
+        <v>560</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>20</v>
@@ -17558,13 +17593,13 @@
         <v>20</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>572</v>
+        <v>20</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>573</v>
+        <v>20</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>20</v>
@@ -17582,13 +17617,13 @@
         <v>20</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>20</v>
@@ -17611,10 +17646,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17637,22 +17672,24 @@
         <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q136" s="2"/>
+      <c r="Q136" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="R136" t="s" s="2">
         <v>20</v>
       </c>
@@ -17675,10 +17712,10 @@
         <v>159</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>20</v>
@@ -17696,7 +17733,7 @@
         <v>20</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -17725,10 +17762,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17739,7 +17776,7 @@
         <v>77</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>20</v>
@@ -17751,16 +17788,16 @@
         <v>89</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>532</v>
+        <v>147</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -17786,13 +17823,13 @@
         <v>20</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>20</v>
+        <v>574</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>20</v>
@@ -17810,13 +17847,13 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>20</v>
@@ -17839,10 +17876,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17865,22 +17902,22 @@
         <v>89</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>473</v>
+        <v>147</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q138" t="s" s="2">
-        <v>587</v>
-      </c>
+      <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
         <v>20</v>
       </c>
@@ -17900,13 +17937,13 @@
         <v>20</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>20</v>
+        <v>579</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>20</v>
@@ -17924,7 +17961,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
@@ -17945,7 +17982,7 @@
         <v>20</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>408</v>
+        <v>20</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>20</v>
@@ -17953,10 +17990,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17967,7 +18004,7 @@
         <v>77</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>20</v>
@@ -17976,18 +18013,20 @@
         <v>20</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>103</v>
+        <v>582</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18012,13 +18051,13 @@
         <v>20</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>20</v>
+        <v>585</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>20</v>
+        <v>586</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>20</v>
@@ -18036,19 +18075,19 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>105</v>
+        <v>581</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>20</v>
@@ -18057,7 +18096,7 @@
         <v>20</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>20</v>
@@ -18065,14 +18104,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18088,19 +18127,19 @@
         <v>20</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>110</v>
+        <v>588</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>111</v>
+        <v>589</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>112</v>
+        <v>590</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18126,13 +18165,13 @@
         <v>20</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>20</v>
+        <v>591</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>20</v>
+        <v>592</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>20</v>
@@ -18150,7 +18189,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>116</v>
+        <v>587</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
@@ -18162,7 +18201,7 @@
         <v>20</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>20</v>
@@ -18171,7 +18210,7 @@
         <v>20</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>20</v>
@@ -18179,46 +18218,44 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J141" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>109</v>
+        <v>544</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>480</v>
+        <v>594</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>481</v>
+        <v>595</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>20</v>
       </c>
@@ -18266,19 +18303,19 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>482</v>
+        <v>593</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>20</v>
@@ -18287,7 +18324,7 @@
         <v>20</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>20</v>
@@ -18295,10 +18332,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18306,10 +18343,10 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>20</v>
@@ -18321,20 +18358,22 @@
         <v>89</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>169</v>
+        <v>475</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q142" s="2"/>
+      <c r="Q142" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="R142" t="s" s="2">
         <v>20</v>
       </c>
@@ -18354,13 +18393,13 @@
         <v>20</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>594</v>
+        <v>20</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>595</v>
+        <v>20</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>20</v>
@@ -18378,13 +18417,13 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>20</v>
@@ -18399,7 +18438,7 @@
         <v>20</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>20</v>
@@ -18407,10 +18446,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18418,7 +18457,7 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>88</v>
@@ -18430,16 +18469,16 @@
         <v>20</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>597</v>
+        <v>102</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>598</v>
+        <v>103</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>599</v>
+        <v>104</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18490,10 +18529,10 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>596</v>
+        <v>105</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>88</v>
@@ -18502,7 +18541,7 @@
         <v>20</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>20</v>
@@ -18511,7 +18550,7 @@
         <v>20</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>20</v>
@@ -18519,14 +18558,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18545,15 +18584,17 @@
         <v>20</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>601</v>
+        <v>110</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N144" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>20</v>
@@ -18602,7 +18643,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>600</v>
+        <v>116</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>77</v>
@@ -18614,23 +18655,475 @@
         <v>20</v>
       </c>
       <c r="AJ144" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK144" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN144" t="s" s="2">
+      <c r="AK146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN148" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN144">
+  <autoFilter ref="A1:AN148">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18640,7 +19133,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI147">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
